--- a/workbooks/02 Formulas 1 - Formula Basics.xlsx
+++ b/workbooks/02 Formulas 1 - Formula Basics.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="695">
   <si>
     <t>Challenge</t>
   </si>
@@ -426,88 +426,97 @@
     <t>T2</t>
   </si>
   <si>
+    <t>Which move is this? Arithmetic: add, subtract, multiply, divide, power.</t>
+  </si>
+  <si>
+    <t>F1-1 Power Up T3</t>
+  </si>
+  <si>
+    <t>Multiply before you add.</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Which move is this? Order: parentheses, then ^, then * and /, then + and -.</t>
+  </si>
+  <si>
+    <t>F1-1 Power Up T4</t>
+  </si>
+  <si>
+    <t>Start with = then the two cell addresses.</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>Pick the formula that multiplies cell B2 by cell C2.</t>
+  </si>
+  <si>
+    <t>CHALLENGES · recall it, then do it</t>
+  </si>
+  <si>
+    <t>▶ Open F1-1 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F1-1 Power Up C1</t>
+  </si>
+  <si>
+    <t>EQUALS</t>
+  </si>
+  <si>
+    <t>EQUALSIGN</t>
+  </si>
+  <si>
+    <t>EQUALSSIGN</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>F1-1 Power Up C2</t>
+  </si>
+  <si>
+    <t>CARET</t>
+  </si>
+  <si>
+    <t>^</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>Which operator raises a number to a power?</t>
   </si>
   <si>
-    <t>F1-1 Power Up T3</t>
-  </si>
-  <si>
-    <t>Multiply before you add.</t>
-  </si>
-  <si>
-    <t>T3</t>
+    <t>F1-1 Power Up C3</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>C3</t>
   </si>
   <si>
     <t>What does =2+3*4 return?</t>
   </si>
   <si>
-    <t>F1-1 Power Up T4</t>
-  </si>
-  <si>
-    <t>Start with = then the two cell addresses.</t>
-  </si>
-  <si>
-    <t>T4</t>
+    <t>F1-1 Power Up C4</t>
+  </si>
+  <si>
+    <t>=C2*B2</t>
+  </si>
+  <si>
+    <t>B2*C2</t>
+  </si>
+  <si>
+    <t>C2*B2</t>
+  </si>
+  <si>
+    <t>C4</t>
   </si>
   <si>
     <t>Type the formula that multiplies cell B2 by cell C2.</t>
-  </si>
-  <si>
-    <t>CHALLENGES · recall it, then do it</t>
-  </si>
-  <si>
-    <t>▶ Open F1-1 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F1-1 Power Up C1</t>
-  </si>
-  <si>
-    <t>EQUALS</t>
-  </si>
-  <si>
-    <t>EQUALSIGN</t>
-  </si>
-  <si>
-    <t>EQUALSSIGN</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>F1-1 Power Up C2</t>
-  </si>
-  <si>
-    <t>CARET</t>
-  </si>
-  <si>
-    <t>^</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>F1-1 Power Up C3</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>F1-1 Power Up C4</t>
-  </si>
-  <si>
-    <t>=C2*B2</t>
-  </si>
-  <si>
-    <t>B2*C2</t>
-  </si>
-  <si>
-    <t>C2*B2</t>
-  </si>
-  <si>
-    <t>C4</t>
   </si>
   <si>
     <t>F1-1 Power Up C5</t>
@@ -1609,55 +1618,61 @@
     <t>Put $ before the column and the row.</t>
   </si>
   <si>
+    <t>Which move is this? An absolute reference never shifts when the formula is copied.</t>
+  </si>
+  <si>
+    <t>F1-3 Anchors T2</t>
+  </si>
+  <si>
+    <t>The $ goes right before 16.</t>
+  </si>
+  <si>
+    <t>Which move is this? Mixed reference: lock only the column ($A1) or only the row (A$1).</t>
+  </si>
+  <si>
+    <t>F1-3 Anchors T3</t>
+  </si>
+  <si>
+    <t>A function key between F3 and F5.</t>
+  </si>
+  <si>
+    <t>Ctrl+Shift+A</t>
+  </si>
+  <si>
+    <t>Which key adds or cycles the $ signs on a reference you are editing?</t>
+  </si>
+  <si>
+    <t>F1-3 Anchors T4</t>
+  </si>
+  <si>
+    <t>D for Down.</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Which keys copy the top cell down into the selected cells?</t>
+  </si>
+  <si>
+    <t>▶ Open F1-3 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>F1-3 Anchors C1</t>
+  </si>
+  <si>
+    <t>$E$6</t>
+  </si>
+  <si>
     <t>Type the absolute version of the reference E6.</t>
   </si>
   <si>
-    <t>F1-3 Anchors T2</t>
-  </si>
-  <si>
-    <t>The $ goes right before 16.</t>
+    <t>F1-3 Anchors C2</t>
+  </si>
+  <si>
+    <t>C$16</t>
   </si>
   <si>
     <t>Type a reference to C16 that locks only the row.</t>
-  </si>
-  <si>
-    <t>F1-3 Anchors T3</t>
-  </si>
-  <si>
-    <t>A function key between F3 and F5.</t>
-  </si>
-  <si>
-    <t>Ctrl+Shift+A</t>
-  </si>
-  <si>
-    <t>Which key adds or cycles the $ signs on a reference you are editing?</t>
-  </si>
-  <si>
-    <t>F1-3 Anchors T4</t>
-  </si>
-  <si>
-    <t>D for Down.</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>Which keys copy the top cell down into the selected cells?</t>
-  </si>
-  <si>
-    <t>▶ Open F1-3 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>F1-3 Anchors C1</t>
-  </si>
-  <si>
-    <t>$E$6</t>
-  </si>
-  <si>
-    <t>F1-3 Anchors C2</t>
-  </si>
-  <si>
-    <t>C$16</t>
   </si>
   <si>
     <t>F1-3 Anchors C3</t>
@@ -3554,7 +3569,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3564,12 +3579,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3579,32 +3594,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3614,30 +3629,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('F1-1 Power Up'!$G$14:$G$37)&amp;" / 170"</f>
@@ -3652,15 +3667,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('F1-2 Big Six'!$G$17:$G$51)&amp;" / 280"</f>
@@ -3675,15 +3690,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('F1-3 Anchors'!$G$14:$G$40)&amp;" / 200"</f>
@@ -3698,15 +3713,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('F1-4 Precision'!$G$13:$G$33)&amp;" / 140"</f>
@@ -3721,15 +3736,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM('F1-5 X-Ray'!$G$15:$G$42)&amp;" / 210"</f>
@@ -3744,15 +3759,15 @@
         <v>NEW</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C18" s="9" cm="1" t="str">
         <f t="array" ref="C18">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3767,12 +3782,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">(SUM('F1-1 Power Up'!$G$14:$G$37)+SUM('F1-2 Big Six'!$G$17:$G$51)+SUM('F1-3 Anchors'!$G$14:$G$40)+SUM('F1-4 Precision'!$G$13:$G$33)+SUM('F1-5 X-Ray'!$G$15:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 1160"</f>
@@ -3781,19 +3796,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">_xlfn.LET(_xlpm.p,(SUM('F1-1 Power Up'!$G$14:$G$37)+SUM('F1-2 Big Six'!$G$17:$G$51)+SUM('F1-3 Anchors'!$G$14:$G$40)+SUM('F1-4 Precision'!$G$13:$G$33)+SUM('F1-5 X-Ray'!$G$15:$G$42)+SUM(Boss!$G$14:$G$33))/1160,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=15),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 15)","—")</f>
@@ -3802,7 +3817,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="7" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
         <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3811,7 +3826,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="13" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -3849,7 +3864,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3860,7 +3875,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -3912,10 +3927,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="67" customHeight="1">
@@ -3923,10 +3938,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="67" customHeight="1">
@@ -3934,10 +3949,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="67" customHeight="1">
@@ -3945,21 +3960,21 @@
         <v>34</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="51.25" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22" customHeight="1">
@@ -4001,7 +4016,7 @@
         <v>47</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -4023,7 +4038,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -4045,7 +4060,7 @@
         <v>57</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -4067,7 +4082,7 @@
         <v>62</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -4089,7 +4104,7 @@
         <v>67</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -4108,10 +4123,10 @@
     </row>
     <row r="20" spans="1:7" ht="19.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -4130,10 +4145,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -4189,7 +4204,7 @@
         <v>73</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -4211,7 +4226,7 @@
         <v>78</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -4233,7 +4248,7 @@
         <v>82</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -4255,7 +4270,7 @@
         <v>86</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -4274,10 +4289,10 @@
     </row>
     <row r="29" spans="1:7" ht="19.75" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -4307,7 +4322,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="B32" s="11" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4338,7 +4353,7 @@
         <v>94</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -4360,7 +4375,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -4379,10 +4394,10 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -4401,10 +4416,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -4423,10 +4438,10 @@
     </row>
     <row r="38" spans="1:7" ht="19.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -4445,10 +4460,10 @@
     </row>
     <row r="39" spans="1:7" ht="67" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
@@ -4467,10 +4482,10 @@
     </row>
     <row r="40" spans="1:7" ht="67" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" cm="1" t="str">
@@ -4489,13 +4504,13 @@
     </row>
     <row r="41" spans="1:7" ht="51.25" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(ISBLANK('F1-5 Arena'!$G$8),"",IF(NOT(_xlfn.ISFORMULA('F1-5 Arena'!$G$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-5 Arena'!$G$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-5 Arena'!$G$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-5 Arena'!$G$8),ABS('F1-5 Arena'!$G$8-Key!$C$100)&lt;=1E-9*MAX(1,ABS(Key!$C$100))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-5 Arena'!$G$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGE")))))</f>
@@ -4513,13 +4528,13 @@
     </row>
     <row r="42" spans="1:7" ht="67" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(ISBLANK('F1-5 Arena'!$G$9),"",IF(NOT(_xlfn.ISFORMULA('F1-5 Arena'!$G$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-5 Arena'!$G$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-5 Arena'!$G$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-5 Arena'!$G$9),ABS('F1-5 Arena'!$G$9-Key!$C$101)&lt;=1E-9*MAX(1,ABS(Key!$C$101))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-5 Arena'!$G$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND")))))</f>
@@ -4665,7 +4680,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4678,21 +4693,21 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="27" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4726,7 +4741,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G8" s="28"/>
     </row>
@@ -4739,7 +4754,7 @@
         <v>45</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G9" s="28"/>
     </row>
@@ -4798,7 +4813,7 @@
     </row>
     <row r="19" spans="8:8">
       <c r="H19" s="7" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="8:8">
@@ -4834,7 +4849,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4845,7 +4860,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -4864,7 +4879,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -4875,19 +4890,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -4896,7 +4911,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C9" s="31">
         <v>15</v>
@@ -4904,7 +4919,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('F1-1 Power Up'!$G$14:$G$37)&gt;=170*0.5,SUM('F1-2 Big Six'!$G$17:$G$51)&gt;=280*0.5,SUM('F1-3 Anchors'!$G$14:$G$40)&gt;=200*0.5,SUM('F1-4 Precision'!$G$13:$G$33)&gt;=140*0.5,SUM('F1-5 X-Ray'!$G$15:$G$42)&gt;=210*0.5),"OPEN","LOCKED")</f>
@@ -4917,7 +4932,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -4951,7 +4966,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which keys switch between showing results and showing formulas?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4974,7 +4989,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which key edits the active cell and color-codes its references?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -4997,7 +5012,7 @@
     </row>
     <row r="16" spans="1:7" ht="51.25" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","While typing a function name, which key inserts the highlighted AutoComplete suggestion?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5020,7 +5035,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B17" s="32" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which keys insert a function's argument names after you type its name?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5066,7 +5081,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which function adds up a range of numbers?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5089,7 +5104,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which function returns the mean of a range?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5112,7 +5127,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which function returns the largest number in a range?  (from F1-2 Big Six)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5135,7 +5150,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5146,7 +5161,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5174,14 +5189,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In J8, total the Qty column (E6:E15) with SUM.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$8),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$8),ABS('Boss Arena'!$J$8-Key!$C$110)&lt;=1E-9*MAX(1,ABS(Key!$C$110))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUM"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUM"))))),"LOCKED")</f>
@@ -5199,14 +5214,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In J9, average the Price column with AVERAGE.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$9),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$9),ABS('Boss Arena'!$J$9-Key!$C$111)&lt;=1E-9*MAX(1,ABS(Key!$C$111))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGE"))))),"LOCKED")</f>
@@ -5224,14 +5239,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","In J10, find the largest Qty with MAX.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$10),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$10),ABS('Boss Arena'!$J$10-Key!$C$112)&lt;=1E-9*MAX(1,ABS(Key!$C$112))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MAX"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use MAX"))))),"LOCKED")</f>
@@ -5249,14 +5264,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","In J11, count the Ratings that are numbers (F6:F15).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$11),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$11),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$11),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$11),ABS('Boss Arena'!$J$11-Key!$C$113)&lt;=1E-9*MAX(1,ABS(Key!$C$113))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNT"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$11)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNT"))))),"LOCKED")</f>
@@ -5274,14 +5289,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","In G6 calculate the profit: (Price - Cost) × Qty. Fill it down to G15 with Ctrl+D.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$G$6,'Boss Arena'!$G$7,'Boss Arena'!$G$8,'Boss Arena'!$G$9,'Boss Arena'!$G$10,'Boss Arena'!$G$11,'Boss Arena'!$G$12,'Boss Arena'!$G$13,'Boss Arena'!$G$14,'Boss Arena'!$G$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$G$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$G$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$G$6),ISERROR('Boss Arena'!$G$7),ISERROR('Boss Arena'!$G$8),ISERROR('Boss Arena'!$G$9),ISERROR('Boss Arena'!$G$10),ISERROR('Boss Arena'!$G$11),ISERROR('Boss Arena'!$G$12),ISERROR('Boss Arena'!$G$13),ISERROR('Boss Arena'!$G$14),ISERROR('Boss Arena'!$G$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$G$6),ABS('Boss Arena'!$G$6-Key!$E$114)&lt;=1E-9*MAX(1,ABS(Key!$E$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$7),ABS('Boss Arena'!$G$7-Key!$F$114)&lt;=1E-9*MAX(1,ABS(Key!$F$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$8),ABS('Boss Arena'!$G$8-Key!$G$114)&lt;=1E-9*MAX(1,ABS(Key!$G$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$9),ABS('Boss Arena'!$G$9-Key!$H$114)&lt;=1E-9*MAX(1,ABS(Key!$H$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$10),ABS('Boss Arena'!$G$10-Key!$I$114)&lt;=1E-9*MAX(1,ABS(Key!$I$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$11),ABS('Boss Arena'!$G$11-Key!$J$114)&lt;=1E-9*MAX(1,ABS(Key!$J$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$12),ABS('Boss Arena'!$G$12-Key!$K$114)&lt;=1E-9*MAX(1,ABS(Key!$K$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$13),ABS('Boss Arena'!$G$13-Key!$L$114)&lt;=1E-9*MAX(1,ABS(Key!$L$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$14),ABS('Boss Arena'!$G$14-Key!$M$114)&lt;=1E-9*MAX(1,ABS(Key!$M$114))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$G$15),ABS('Boss Arena'!$G$15-Key!$N$114)&lt;=1E-9*MAX(1,ABS(Key!$N$114))),FALSE))),"✘ TRY AGAIN","✔ CLEAR")))),"LOCKED")</f>
@@ -5299,14 +5314,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In H6 calculate the tax: Price × the rate in K6. Lock K6 with F4, then fill down to H15.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$H$6,'Boss Arena'!$H$7,'Boss Arena'!$H$8,'Boss Arena'!$H$9,'Boss Arena'!$H$10,'Boss Arena'!$H$11,'Boss Arena'!$H$12,'Boss Arena'!$H$13,'Boss Arena'!$H$14,'Boss Arena'!$H$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$H$6)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$7)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$8)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$9)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$10)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$11)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$12)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$13)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$14)),NOT(_xlfn.ISFORMULA('Boss Arena'!$H$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$H$6),ISERROR('Boss Arena'!$H$7),ISERROR('Boss Arena'!$H$8),ISERROR('Boss Arena'!$H$9),ISERROR('Boss Arena'!$H$10),ISERROR('Boss Arena'!$H$11),ISERROR('Boss Arena'!$H$12),ISERROR('Boss Arena'!$H$13),ISERROR('Boss Arena'!$H$14),ISERROR('Boss Arena'!$H$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$H$6),ABS('Boss Arena'!$H$6-Key!$E$115)&lt;=1E-9*MAX(1,ABS(Key!$E$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$7),ABS('Boss Arena'!$H$7-Key!$F$115)&lt;=1E-9*MAX(1,ABS(Key!$F$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$8),ABS('Boss Arena'!$H$8-Key!$G$115)&lt;=1E-9*MAX(1,ABS(Key!$G$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$9),ABS('Boss Arena'!$H$9-Key!$H$115)&lt;=1E-9*MAX(1,ABS(Key!$H$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$10),ABS('Boss Arena'!$H$10-Key!$I$115)&lt;=1E-9*MAX(1,ABS(Key!$I$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$11),ABS('Boss Arena'!$H$11-Key!$J$115)&lt;=1E-9*MAX(1,ABS(Key!$J$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$12),ABS('Boss Arena'!$H$12-Key!$K$115)&lt;=1E-9*MAX(1,ABS(Key!$K$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$13),ABS('Boss Arena'!$H$13-Key!$L$115)&lt;=1E-9*MAX(1,ABS(Key!$L$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$14),ABS('Boss Arena'!$H$14-Key!$M$115)&lt;=1E-9*MAX(1,ABS(Key!$M$115))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$H$15),ABS('Boss Arena'!$H$15-Key!$N$115)&lt;=1E-9*MAX(1,ABS(Key!$N$115))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('Boss Arena'!$H$6))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)"))))),"LOCKED")</f>
@@ -5324,14 +5339,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","In J12, average the Price column and round to 1 decimal in one formula.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(ISBLANK('Boss Arena'!$J$12),"",IF(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$12)),"✘ That's a typed value · enter a formula",IF(ISERROR('Boss Arena'!$J$12),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('Boss Arena'!$J$12),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$J$12),ABS('Boss Arena'!$J$12-Key!$C$116)&lt;=1E-9*MAX(1,ABS(Key!$C$116))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$12))))),OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGE"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$J$12)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND and AVERAGE"))))),"LOCKED")</f>
@@ -5349,7 +5364,7 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Press Ctrl+` in the Boss Arena. One cell in L6:L15 was typed over. Type its address.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5472,7 +5487,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -5485,10 +5500,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5496,7 +5511,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>10</v>
@@ -5505,24 +5520,24 @@
         <v>11</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="5" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C6" s="5">
         <v>12</v>
@@ -5548,7 +5563,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="5" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C7" s="5">
         <v>3</v>
@@ -5571,7 +5586,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="5" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C8" s="5">
         <v>85</v>
@@ -5583,12 +5598,12 @@
         <v>2</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G8" s="28"/>
       <c r="H8" s="28"/>
       <c r="I8" s="5" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="J8" s="28"/>
       <c r="L8" s="5" cm="1">
@@ -5598,7 +5613,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C9" s="5">
         <v>40</v>
@@ -5615,7 +5630,7 @@
       <c r="G9" s="28"/>
       <c r="H9" s="28"/>
       <c r="I9" s="5" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="J9" s="28"/>
       <c r="L9" s="5">
@@ -5624,7 +5639,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="5" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C10" s="5">
         <v>0.4</v>
@@ -5641,7 +5656,7 @@
       <c r="G10" s="28"/>
       <c r="H10" s="28"/>
       <c r="I10" s="5" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="J10" s="28"/>
       <c r="L10" s="5" cm="1">
@@ -5651,7 +5666,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="5" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C11" s="5">
         <v>6</v>
@@ -5668,7 +5683,7 @@
       <c r="G11" s="28"/>
       <c r="H11" s="28"/>
       <c r="I11" s="5" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="J11" s="28"/>
       <c r="L11" s="5" cm="1">
@@ -5678,7 +5693,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="5" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C12" s="5">
         <v>10</v>
@@ -5690,12 +5705,12 @@
         <v>6</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G12" s="28"/>
       <c r="H12" s="28"/>
       <c r="I12" s="5" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="J12" s="28"/>
       <c r="L12" s="5" cm="1">
@@ -5705,7 +5720,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="5" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C13" s="5">
         <v>4</v>
@@ -5728,7 +5743,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="5" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C14" s="5">
         <v>30</v>
@@ -5751,7 +5766,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="5" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C15" s="5">
         <v>22</v>
@@ -5797,7 +5812,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5805,343 +5820,343 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>77</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="35.5" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -6356,18 +6371,18 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
@@ -6376,21 +6391,21 @@
         <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" cm="1">
         <f t="array" ref="C15">'F1-1 Arena'!$C$6*'F1-1 Arena'!$D$6</f>
@@ -6399,10 +6414,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C16" cm="1">
         <f t="array" ref="C16">('F1-1 Arena'!$C$7+3)*'F1-1 Arena'!$D$7</f>
@@ -6411,10 +6426,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C17" cm="1">
         <f t="array" ref="C17">'F1-1 Arena'!$D$8^2</f>
@@ -6423,10 +6438,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -6434,7 +6449,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
@@ -6454,7 +6469,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
@@ -6468,18 +6483,18 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
         <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B22" t="s">
         <v>85</v>
@@ -6488,438 +6503,438 @@
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F24" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F25" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E26" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F28" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G28" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H29" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H30" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B31" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F31" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B32" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F32" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G33" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H33" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B34" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E34" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F34" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G34" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H34" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I34" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J34" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E35" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F35" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G35" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J35" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E36" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F36" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G36" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H36" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I36" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J36" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F37" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G37" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H37" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I37" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J37" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F38" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G38" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H38" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I38" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J38" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E39" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F39" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G39" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H39" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I39" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J39" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E40" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C41" cm="1">
         <f t="array" ref="C41">SUM('F1-2 Arena'!$C$6:$C$17)</f>
@@ -6928,10 +6943,10 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C42" cm="1">
         <f t="array" ref="C42">AVERAGE('F1-2 Arena'!$C$6:$C$17)</f>
@@ -6940,10 +6955,10 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C43" cm="1">
         <f t="array" ref="C43">MAX('F1-2 Arena'!$C$6:$C$17)</f>
@@ -6952,10 +6967,10 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C44" cm="1">
         <f t="array" ref="C44">MIN('F1-2 Arena'!$C$6:$C$17)</f>
@@ -6964,10 +6979,10 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C45" cm="1">
         <f t="array" ref="C45">COUNT('F1-2 Arena'!$D$6:$D$17)</f>
@@ -6976,10 +6991,10 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C46" cm="1">
         <f t="array" ref="C46">COUNTA('F1-2 Arena'!$D$6:$D$17)</f>
@@ -6988,216 +7003,216 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E47" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F47" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G47" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H47" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I47" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J47" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E48" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F48" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G48" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H48" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I48" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J48" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E49" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F49" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G49" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J49" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E50" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F50" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H50" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I50" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J50" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E51" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F51" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G51" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H51" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I51" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J51" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E52" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F52" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G52" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I52" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J52" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E54" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E55" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E56" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F56" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G56" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C57" t="s">
         <v>72</v>
@@ -7217,10 +7232,10 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C58" t="s">
         <v>77</v>
@@ -7240,100 +7255,100 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E59" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H59" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B60" t="s">
+        <v>368</v>
+      </c>
+      <c r="C60" t="s">
+        <v>326</v>
+      </c>
+      <c r="E60" t="s">
+        <v>242</v>
+      </c>
+      <c r="F60" t="s">
+        <v>369</v>
+      </c>
+      <c r="G60" t="s">
+        <v>326</v>
+      </c>
+      <c r="H60" t="s">
         <v>365</v>
-      </c>
-      <c r="C60" t="s">
-        <v>323</v>
-      </c>
-      <c r="E60" t="s">
-        <v>239</v>
-      </c>
-      <c r="F60" t="s">
-        <v>366</v>
-      </c>
-      <c r="G60" t="s">
-        <v>323</v>
-      </c>
-      <c r="H60" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E61" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E62" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B63" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E63" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E64" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E65" cm="1">
         <f t="array" ref="E65">'F1-3 Arena'!$B$6*'F1-3 Arena'!$E$6</f>
@@ -7370,10 +7385,10 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E66" cm="1">
         <f t="array" ref="E66">'F1-3 Arena'!$B$17*(1-'F1-3 Arena'!$C$16)</f>
@@ -7398,201 +7413,201 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B67" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E67" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E68" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E69" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E70" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B71" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C71" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E71" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G71" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H71" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B72" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E72" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F72" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G72" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H72" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B73" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C73" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E73" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F73" t="s">
+        <v>169</v>
+      </c>
+      <c r="G73" t="s">
+        <v>235</v>
+      </c>
+      <c r="H73" t="s">
         <v>166</v>
-      </c>
-      <c r="G73" t="s">
-        <v>232</v>
-      </c>
-      <c r="H73" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B74" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E74" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F74" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G74" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I74" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J74" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B75" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E75" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F75" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G75" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H75" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I75" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J75" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E76" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F76" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G76" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I76" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="J76" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B77" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C77" cm="1">
         <f t="array" ref="C77">ROUND('F1-4 Arena'!$B$6,2)</f>
@@ -7601,10 +7616,10 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B78" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C78" cm="1">
         <f t="array" ref="C78">ROUNDUP('F1-4 Arena'!$B$7,0)</f>
@@ -7613,10 +7628,10 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B79" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C79" cm="1">
         <f t="array" ref="C79">ROUNDDOWN('F1-4 Arena'!$B$8,1)</f>
@@ -7625,10 +7640,10 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C80" cm="1">
         <f t="array" ref="C80">ROUND('F1-4 Arena'!$B$9,-2)</f>
@@ -7637,85 +7652,85 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B81" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E81" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F81" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G81" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="H81" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I81" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J81" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E82" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F82" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G82" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="H82" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I82" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J82" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B83" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E83" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F83" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G83" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H83" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I83" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="J83" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s">
         <v>71</v>
@@ -7735,7 +7750,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s">
         <v>76</v>
@@ -7749,18 +7764,18 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s">
         <v>81</v>
       </c>
       <c r="E86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s">
         <v>85</v>
@@ -7769,225 +7784,225 @@
         <v>36</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G87" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C88" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E88" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F88" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G88" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H88" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B89" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C89" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F89" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G89" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H89" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C90" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E90" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F90" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G90" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H90" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B91" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C91" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E91" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F91" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G91" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H91" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B92" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C92" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F92" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G92" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H92" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B93" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E93" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F93" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G93" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H93" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B94" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E94" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B95" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E95" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E96" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F96" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B97" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E97" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C98" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B99" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C99" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B100" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C100" cm="1">
         <f t="array" ref="C100">AVERAGE('F1-5 Arena'!$C$6:$C$15)</f>
@@ -7996,10 +8011,10 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B101" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C101" cm="1">
         <f t="array" ref="C101">ROUND('F1-5 Arena'!$E$6/7,1)</f>
@@ -8008,155 +8023,155 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E102" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F102" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G102" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="H102" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E104" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="E105" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F105" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B106" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="E106" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E107" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F107" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G107" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H107" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I107" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J107" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B108" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E108" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F108" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G108" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H108" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I108" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J108" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B109" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E109" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F109" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G109" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H109" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J109" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B110" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C110" cm="1">
         <f t="array" ref="C110">SUM('Boss Arena'!$E$6:$E$15)</f>
@@ -8165,10 +8180,10 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B111" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C111" cm="1">
         <f t="array" ref="C111">AVERAGE('Boss Arena'!$D$6:$D$15)</f>
@@ -8177,10 +8192,10 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B112" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C112" cm="1">
         <f t="array" ref="C112">MAX('Boss Arena'!$E$6:$E$15)</f>
@@ -8189,10 +8204,10 @@
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B113" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C113" cm="1">
         <f t="array" ref="C113">COUNT('Boss Arena'!$F$6:$F$15)</f>
@@ -8201,10 +8216,10 @@
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="B114" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E114" cm="1">
         <f t="array" ref="E114">('Boss Arena'!$D$6-'Boss Arena'!$C$6)*'Boss Arena'!$E$6</f>
@@ -8249,10 +8264,10 @@
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B115" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E115" cm="1">
         <f t="array" ref="E115">'Boss Arena'!$D$6*'Boss Arena'!$K$6</f>
@@ -8297,10 +8312,10 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B116" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C116" cm="1">
         <f t="array" ref="C116">ROUND(AVERAGE('Boss Arena'!$D$6:$D$15),1)</f>
@@ -8309,13 +8324,13 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B117" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C117" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -8343,7 +8358,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8354,7 +8369,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8645,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="19.75" customHeight="1">
+    <row r="23" spans="1:7" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
         <v>78</v>
       </c>
@@ -8667,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="19.75" customHeight="1">
+    <row r="24" spans="1:7" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
         <v>82</v>
       </c>
@@ -8777,7 +8792,7 @@
         <v>98</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -8796,10 +8811,10 @@
     </row>
     <row r="32" spans="1:7" ht="19.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -8818,10 +8833,10 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -8840,13 +8855,13 @@
     </row>
     <row r="34" spans="1:7" ht="51.25" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D34" s="21" cm="1" t="str">
         <f t="array" ref="D34">IF(ISBLANK('F1-1 Arena'!$F$6),"",IF(NOT(_xlfn.ISFORMULA('F1-1 Arena'!$F$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-1 Arena'!$F$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-1 Arena'!$F$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-1 Arena'!$F$6),ABS('F1-1 Arena'!$F$6-Key!$C$15)&lt;=1E-9*MAX(1,ABS(Key!$C$15))),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -8864,13 +8879,13 @@
     </row>
     <row r="35" spans="1:7" ht="51.25" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D35" s="21" cm="1" t="str">
         <f t="array" ref="D35">IF(ISBLANK('F1-1 Arena'!$F$7),"",IF(NOT(_xlfn.ISFORMULA('F1-1 Arena'!$F$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-1 Arena'!$F$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-1 Arena'!$F$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-1 Arena'!$F$7),ABS('F1-1 Arena'!$F$7-Key!$C$16)&lt;=1E-9*MAX(1,ABS(Key!$C$16))),FALSE))),"✘ TRY AGAIN","✔ CLEAR"))))</f>
@@ -8888,13 +8903,13 @@
     </row>
     <row r="36" spans="1:7" ht="35.5" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D36" s="21" cm="1" t="str">
         <f t="array" ref="D36">IF(ISBLANK('F1-1 Arena'!$F$8),"",IF(NOT(_xlfn.ISFORMULA('F1-1 Arena'!$F$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-1 Arena'!$F$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-1 Arena'!$F$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-1 Arena'!$F$8),ABS('F1-1 Arena'!$F$8-Key!$C$17)&lt;=1E-9*MAX(1,ABS(Key!$C$17))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("^",_xlfn.FORMULATEXT('F1-1 Arena'!$F$8))),"✔ CLEAR","✘ CLOSE · your formula needs ^")))))</f>
@@ -8912,10 +8927,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -9165,7 +9180,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9176,7 +9191,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -9228,10 +9243,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -9239,10 +9254,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -9250,10 +9265,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="35.5" customHeight="1">
@@ -9261,43 +9276,43 @@
         <v>34</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="51.25" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="51.25" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="67" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="22" customHeight="1">
@@ -9339,7 +9354,7 @@
         <v>47</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -9361,7 +9376,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -9383,7 +9398,7 @@
         <v>57</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -9405,7 +9420,7 @@
         <v>62</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -9427,7 +9442,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -9446,10 +9461,10 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -9468,10 +9483,10 @@
     </row>
     <row r="23" spans="1:7" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -9490,10 +9505,10 @@
     </row>
     <row r="24" spans="1:7" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21" cm="1" t="str">
@@ -9549,7 +9564,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -9571,7 +9586,7 @@
         <v>78</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -9593,7 +9608,7 @@
         <v>82</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -9615,7 +9630,7 @@
         <v>86</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -9634,10 +9649,10 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -9656,10 +9671,10 @@
     </row>
     <row r="33" spans="1:7" ht="19.75" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -9678,10 +9693,10 @@
     </row>
     <row r="34" spans="1:7" ht="19.75" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -9711,7 +9726,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="B37" s="11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -9742,7 +9757,7 @@
         <v>94</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
@@ -9764,7 +9779,7 @@
         <v>98</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" cm="1" t="str">
@@ -9783,10 +9798,10 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21" cm="1" t="str">
@@ -9805,10 +9820,10 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" cm="1" t="str">
@@ -9827,10 +9842,10 @@
     </row>
     <row r="43" spans="1:7" ht="35.5" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="21" cm="1" t="str">
@@ -9849,10 +9864,10 @@
     </row>
     <row r="44" spans="1:7" ht="19.75" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="21" cm="1" t="str">
@@ -9871,10 +9886,10 @@
     </row>
     <row r="45" spans="1:7" ht="19.75" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" cm="1" t="str">
@@ -9893,13 +9908,13 @@
     </row>
     <row r="46" spans="1:7" ht="51.25" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D46" s="21" cm="1" t="str">
         <f t="array" ref="D46">IF(ISBLANK('F1-2 Arena'!$C$18),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$C$18)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$C$18),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$C$18),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$C$18),ABS('F1-2 Arena'!$C$18-Key!$C$41)&lt;=1E-9*MAX(1,ABS(Key!$C$41))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUM"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$C$18)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUM")))))</f>
@@ -9917,13 +9932,13 @@
     </row>
     <row r="47" spans="1:7" ht="35.5" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D47" s="21" cm="1" t="str">
         <f t="array" ref="D47">IF(ISBLANK('F1-2 Arena'!$G$6),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$G$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$G$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$G$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$G$6),ABS('F1-2 Arena'!$G$6-Key!$C$42)&lt;=1E-9*MAX(1,ABS(Key!$C$42))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"AVERAGE"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$G$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use AVERAGE")))))</f>
@@ -9941,13 +9956,13 @@
     </row>
     <row r="48" spans="1:7" ht="19.75" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D48" s="21" cm="1" t="str">
         <f t="array" ref="D48">IF(ISBLANK('F1-2 Arena'!$G$7),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$G$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$G$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$G$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$G$7),ABS('F1-2 Arena'!$G$7-Key!$C$43)&lt;=1E-9*MAX(1,ABS(Key!$C$43))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MAX"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$G$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use MAX")))))</f>
@@ -9965,13 +9980,13 @@
     </row>
     <row r="49" spans="1:7" ht="19.75" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D49" s="21" cm="1" t="str">
         <f t="array" ref="D49">IF(ISBLANK('F1-2 Arena'!$G$8),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$G$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$G$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$G$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$G$8),ABS('F1-2 Arena'!$G$8-Key!$C$44)&lt;=1E-9*MAX(1,ABS(Key!$C$44))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"MIN"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$G$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use MIN")))))</f>
@@ -9989,13 +10004,13 @@
     </row>
     <row r="50" spans="1:7" ht="35.5" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D50" s="21" cm="1" t="str">
         <f t="array" ref="D50">IF(ISBLANK('F1-2 Arena'!$G$9),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$G$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$G$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$G$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$G$9),ABS('F1-2 Arena'!$G$9-Key!$C$45)&lt;=1E-9*MAX(1,ABS(Key!$C$45))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNT"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$G$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNT")))))</f>
@@ -10013,13 +10028,13 @@
     </row>
     <row r="51" spans="1:7" ht="35.5" customHeight="1">
       <c r="A51" s="18" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D51" s="21" cm="1" t="str">
         <f t="array" ref="D51">IF(ISBLANK('F1-2 Arena'!$G$10),"",IF(NOT(_xlfn.ISFORMULA('F1-2 Arena'!$G$10)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-2 Arena'!$G$10),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-2 Arena'!$G$10),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-2 Arena'!$G$10),ABS('F1-2 Arena'!$G$10-Key!$C$46)&lt;=1E-9*MAX(1,ABS(Key!$C$46))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"COUNTA"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-2 Arena'!$G$10)))))),"✔ CLEAR","✘ CLOSE · right value, but use COUNTA")))))</f>
@@ -10197,7 +10212,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -10210,21 +10225,21 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="27" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>16</v>
@@ -10232,7 +10247,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5">
         <v>420</v>
@@ -10241,13 +10256,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G6" s="28"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C7" s="5">
         <v>515</v>
@@ -10256,28 +10271,28 @@
         <v>5</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G7" s="28"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8" s="5">
         <v>380</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G8" s="28"/>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" s="5">
         <v>610</v>
@@ -10286,13 +10301,13 @@
         <v>2</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G9" s="28"/>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C10" s="5">
         <v>450</v>
@@ -10301,13 +10316,13 @@
         <v>4</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G10" s="28"/>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C11" s="5">
         <v>555</v>
@@ -10318,18 +10333,18 @@
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C12" s="5">
         <v>700</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C13" s="5">
         <v>640</v>
@@ -10340,7 +10355,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="B14" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C14" s="5">
         <v>480</v>
@@ -10351,7 +10366,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="B15" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C15" s="5">
         <v>530</v>
@@ -10362,7 +10377,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C16" s="5">
         <v>690</v>
@@ -10373,7 +10388,7 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C17" s="5">
         <v>720</v>
@@ -10384,7 +10399,7 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C18" s="28"/>
     </row>
@@ -10416,7 +10431,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10427,7 +10442,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -10479,7 +10494,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>72</v>
@@ -10490,7 +10505,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>77</v>
@@ -10501,10 +10516,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="67" customHeight="1">
@@ -10512,10 +10527,10 @@
         <v>34</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
@@ -10557,7 +10572,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -10579,7 +10594,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -10601,7 +10616,7 @@
         <v>57</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -10623,7 +10638,7 @@
         <v>62</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -10645,7 +10660,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -10664,10 +10679,10 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -10686,10 +10701,10 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -10708,10 +10723,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -10730,10 +10745,10 @@
     </row>
     <row r="22" spans="1:7" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -10752,10 +10767,10 @@
     </row>
     <row r="23" spans="1:7" ht="51.25" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -10811,7 +10826,7 @@
         <v>73</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -10833,7 +10848,7 @@
         <v>78</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -10855,7 +10870,7 @@
         <v>82</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -10877,7 +10892,7 @@
         <v>86</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -10907,7 +10922,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -10938,7 +10953,7 @@
         <v>94</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -10960,7 +10975,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -10979,10 +10994,10 @@
     </row>
     <row r="37" spans="1:7" ht="35.5" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -11001,10 +11016,10 @@
     </row>
     <row r="38" spans="1:7" ht="35.5" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -11023,13 +11038,13 @@
     </row>
     <row r="39" spans="1:7" ht="51.25" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
         <f t="array" ref="D39">IF(COUNTA('F1-3 Arena'!$C$6,'F1-3 Arena'!$C$7,'F1-3 Arena'!$C$8,'F1-3 Arena'!$C$9,'F1-3 Arena'!$C$10,'F1-3 Arena'!$C$11,'F1-3 Arena'!$C$12,'F1-3 Arena'!$C$13)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$6)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$7)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$8)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$9)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$10)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$11)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$12)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$13))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F1-3 Arena'!$C$6),ISERROR('F1-3 Arena'!$C$7),ISERROR('F1-3 Arena'!$C$8),ISERROR('F1-3 Arena'!$C$9),ISERROR('F1-3 Arena'!$C$10),ISERROR('F1-3 Arena'!$C$11),ISERROR('F1-3 Arena'!$C$12),ISERROR('F1-3 Arena'!$C$13)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$6),ABS('F1-3 Arena'!$C$6-Key!$E$65)&lt;=1E-9*MAX(1,ABS(Key!$E$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$7),ABS('F1-3 Arena'!$C$7-Key!$F$65)&lt;=1E-9*MAX(1,ABS(Key!$F$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$8),ABS('F1-3 Arena'!$C$8-Key!$G$65)&lt;=1E-9*MAX(1,ABS(Key!$G$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$9),ABS('F1-3 Arena'!$C$9-Key!$H$65)&lt;=1E-9*MAX(1,ABS(Key!$H$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$10),ABS('F1-3 Arena'!$C$10-Key!$I$65)&lt;=1E-9*MAX(1,ABS(Key!$I$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$11),ABS('F1-3 Arena'!$C$11-Key!$J$65)&lt;=1E-9*MAX(1,ABS(Key!$J$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$12),ABS('F1-3 Arena'!$C$12-Key!$K$65)&lt;=1E-9*MAX(1,ABS(Key!$K$65))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$13),ABS('F1-3 Arena'!$C$13-Key!$L$65)&lt;=1E-9*MAX(1,ABS(Key!$L$65))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('F1-3 Arena'!$C$6))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)")))))</f>
@@ -11047,13 +11062,13 @@
     </row>
     <row r="40" spans="1:7" ht="51.25" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(COUNTA('F1-3 Arena'!$C$17,'F1-3 Arena'!$C$18,'F1-3 Arena'!$C$19,'F1-3 Arena'!$C$20,'F1-3 Arena'!$C$21)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$17)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$18)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$19)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$20)),NOT(_xlfn.ISFORMULA('F1-3 Arena'!$C$21))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('F1-3 Arena'!$C$17),ISERROR('F1-3 Arena'!$C$18),ISERROR('F1-3 Arena'!$C$19),ISERROR('F1-3 Arena'!$C$20),ISERROR('F1-3 Arena'!$C$21)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$17),ABS('F1-3 Arena'!$C$17-Key!$E$66)&lt;=1E-9*MAX(1,ABS(Key!$E$66))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$18),ABS('F1-3 Arena'!$C$18-Key!$F$66)&lt;=1E-9*MAX(1,ABS(Key!$F$66))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$19),ABS('F1-3 Arena'!$C$19-Key!$G$66)&lt;=1E-9*MAX(1,ABS(Key!$G$66))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$20),ABS('F1-3 Arena'!$C$20-Key!$H$66)&lt;=1E-9*MAX(1,ABS(Key!$H$66))),FALSE),IFERROR(AND(ISNUMBER('F1-3 Arena'!$C$21),ABS('F1-3 Arena'!$C$21-Key!$I$66)&lt;=1E-9*MAX(1,ABS(Key!$I$66))),FALSE))),"✘ TRY AGAIN",IF(ISNUMBER(FIND("$",_xlfn.FORMULATEXT('F1-3 Arena'!$C$17))),"✔ CLEAR","✘ CLOSE · add $ so it fills correctly (F4)")))))</f>
@@ -11192,7 +11207,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -11205,10 +11220,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -11216,10 +11231,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -11275,7 +11290,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="B16" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C16" s="29">
         <v>0.1</v>
@@ -11345,7 +11360,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11356,7 +11371,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -11408,10 +11423,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="51.25" customHeight="1">
@@ -11419,10 +11434,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="51.25" customHeight="1">
@@ -11430,10 +11445,10 @@
         <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1">
@@ -11475,7 +11490,7 @@
         <v>47</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="21" cm="1" t="str">
@@ -11497,7 +11512,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -11519,7 +11534,7 @@
         <v>57</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -11541,7 +11556,7 @@
         <v>62</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -11597,7 +11612,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -11619,7 +11634,7 @@
         <v>78</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -11641,7 +11656,7 @@
         <v>82</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -11671,7 +11686,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="B25" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -11702,7 +11717,7 @@
         <v>94</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -11724,7 +11739,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -11743,10 +11758,10 @@
     </row>
     <row r="29" spans="1:7" ht="19.75" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -11765,13 +11780,13 @@
     </row>
     <row r="30" spans="1:7" ht="19.75" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF(ISBLANK('F1-4 Arena'!$D$6),"",IF(NOT(_xlfn.ISFORMULA('F1-4 Arena'!$D$6)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-4 Arena'!$D$6),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-4 Arena'!$D$6),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-4 Arena'!$D$6),ABS('F1-4 Arena'!$D$6-Key!$C$77)&lt;=1E-9*MAX(1,ABS(Key!$C$77))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-4 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND")))))</f>
@@ -11789,13 +11804,13 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF(ISBLANK('F1-4 Arena'!$D$7),"",IF(NOT(_xlfn.ISFORMULA('F1-4 Arena'!$D$7)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-4 Arena'!$D$7),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-4 Arena'!$D$7),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-4 Arena'!$D$7),ABS('F1-4 Arena'!$D$7-Key!$C$78)&lt;=1E-9*MAX(1,ABS(Key!$C$78))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUNDUP"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-4 Arena'!$D$7)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUNDUP")))))</f>
@@ -11813,13 +11828,13 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF(ISBLANK('F1-4 Arena'!$D$8),"",IF(NOT(_xlfn.ISFORMULA('F1-4 Arena'!$D$8)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-4 Arena'!$D$8),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-4 Arena'!$D$8),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-4 Arena'!$D$8),ABS('F1-4 Arena'!$D$8-Key!$C$79)&lt;=1E-9*MAX(1,ABS(Key!$C$79))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUNDDOWN"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-4 Arena'!$D$8)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUNDDOWN")))))</f>
@@ -11837,13 +11852,13 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF(ISBLANK('F1-4 Arena'!$D$9),"",IF(NOT(_xlfn.ISFORMULA('F1-4 Arena'!$D$9)),"✘ That's a typed value · enter a formula",IF(ISERROR('F1-4 Arena'!$D$9),"✘ Your formula returns "&amp;IFERROR(CHOOSE(ERROR.TYPE('F1-4 Arena'!$D$9),"#NULL!","#DIV/0!","#VALUE!","#REF!","#NAME?","#NUM!","#N/A","#GETTING_DATA","#SPILL!","#CONNECT!","#BLOCKED!","#UNKNOWN!","#FIELD!","#CALC!"),"an error"),IF(NOT(AND(IFERROR(AND(ISNUMBER('F1-4 Arena'!$D$9),ABS('F1-4 Arena'!$D$9-Key!$C$80)&lt;=1E-9*MAX(1,ABS(Key!$C$80))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"ROUND"&amp;"(",UPPER(_xlfn.FORMULATEXT('F1-4 Arena'!$D$9)))))),"✔ CLEAR","✘ CLOSE · right value, but use ROUND")))))</f>
@@ -11957,7 +11972,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -11970,18 +11985,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="27" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -11989,7 +12004,7 @@
         <v>3.14159</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D6" s="28"/>
     </row>
@@ -11998,7 +12013,7 @@
         <v>2.4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D7" s="28"/>
     </row>
@@ -12007,7 +12022,7 @@
         <v>7.86</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D8" s="28"/>
     </row>
@@ -12016,7 +12031,7 @@
         <v>1234.5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D9" s="28"/>
     </row>

--- a/workbooks/02 Formulas 1 - Formula Basics.xlsx
+++ b/workbooks/02 Formulas 1 - Formula Basics.xlsx
@@ -2729,7 +2729,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ FORMULA BASICS</t>
@@ -3820,7 +3820,7 @@
         <v>643</v>
       </c>
       <c r="B23" s="12" cm="1" t="str">
-        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B23">IFERROR(INDEX($A$13:$A$17,MATCH("☆☆☆",$D$13:$D$17,0))&amp;" "&amp;INDEX($B$13:$B$17,MATCH("☆☆☆",$D$13:$D$17,0)),IF(Start!$E$18="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>F1-1 Power Up</v>
       </c>
     </row>
